--- a/data/hex_xlsx/TIETO.HE.xlsx
+++ b/data/hex_xlsx/TIETO.HE.xlsx
@@ -24148,17 +24148,33 @@
       <c r="O119" s="18">
         <v>835.27</v>
       </c>
-      <c r="P119" s="17"/>
+      <c r="P119" s="18">
+        <v>508.3</v>
+      </c>
       <c r="Q119" s="20">
         <v>8.57</v>
       </c>
-      <c r="R119" s="17"/>
-      <c r="S119" s="17"/>
-      <c r="T119" s="17"/>
-      <c r="U119" s="17"/>
-      <c r="V119" s="17"/>
-      <c r="W119" s="17"/>
-      <c r="X119" s="17"/>
+      <c r="R119" s="18">
+        <v>321.8</v>
+      </c>
+      <c r="S119" s="18">
+        <v>647.53</v>
+      </c>
+      <c r="T119" s="18">
+        <v>768.29</v>
+      </c>
+      <c r="U119" s="18">
+        <v>634.13</v>
+      </c>
+      <c r="V119" s="18">
+        <v>1160.13</v>
+      </c>
+      <c r="W119" s="20">
+        <v>42.84</v>
+      </c>
+      <c r="X119" s="18">
+        <v>172.43</v>
+      </c>
       <c r="Y119" s="17"/>
       <c r="Z119" s="17"/>
       <c r="AA119" s="17"/>
